--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -98,6 +98,29 @@
 每一行必出一个物品
 相同ID表示一个组
 一个组ID进行掉落时，需要把组内掉落包都走一遍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+赌场掉落包
+</t>
         </r>
       </text>
     </comment>
@@ -1144,8 +1167,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
@@ -1257,6 +1280,78 @@
         <v>12</v>
       </c>
     </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>10040</v>
+      </c>
+      <c r="B9"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>10050</v>
+      </c>
+      <c r="B10"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>10060</v>
+      </c>
+      <c r="B11"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10070</v>
+      </c>
+      <c r="B12"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>10080</v>
+      </c>
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>10090</v>
+      </c>
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>10100</v>
+      </c>
+      <c r="B15"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>10110</v>
+      </c>
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>10120</v>
+      </c>
+      <c r="B17"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>10130</v>
+      </c>
+      <c r="B18"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>10140</v>
+      </c>
+      <c r="B19"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>10150</v>
+      </c>
+      <c r="B20"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>序号ID</t>
   </si>
@@ -177,6 +177,36 @@
   </si>
   <si>
     <t>12001_0_10000</t>
+  </si>
+  <si>
+    <t>12002_500</t>
+  </si>
+  <si>
+    <t>12002_1000</t>
+  </si>
+  <si>
+    <t>12002_2000</t>
+  </si>
+  <si>
+    <t>12002_3000</t>
+  </si>
+  <si>
+    <t>12002_5000</t>
+  </si>
+  <si>
+    <t>12002_7500</t>
+  </si>
+  <si>
+    <t>12002_10000</t>
+  </si>
+  <si>
+    <t>12002_12500</t>
+  </si>
+  <si>
+    <t>12002_15000</t>
+  </si>
+  <si>
+    <t>12002_40000</t>
   </si>
 </sst>
 </file>
@@ -836,7 +866,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,6 +883,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1280,77 +1313,137 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
-      <c r="B9"/>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="B9" s="6">
+        <v>10010040</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
-      <c r="B10"/>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="B10" s="6">
+        <v>10010050</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
-      <c r="B11"/>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="B11" s="6">
+        <v>10010060</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
-      <c r="B12"/>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="B12" s="6">
+        <v>10010070</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="B13" s="6">
+        <v>10010080</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
-      <c r="B14"/>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="B14" s="6">
+        <v>10010090</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
-      <c r="B15"/>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="B15" s="6">
+        <v>10010100</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
-      <c r="B16"/>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="B16" s="6">
+        <v>10010110</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
-      <c r="B17"/>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="B17" s="6">
+        <v>10010120</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
-      <c r="B18"/>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="B18" s="6">
+        <v>10010130</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
-      <c r="B19"/>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="B19" s="6">
+        <v>10010140</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
-      <c r="B20"/>
+      <c r="B20" s="6">
+        <v>10010150</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -1318,7 +1318,7 @@
         <v>10040</v>
       </c>
       <c r="B9" s="6">
-        <v>10010040</v>
+        <v>10040</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -1329,7 +1329,7 @@
         <v>10050</v>
       </c>
       <c r="B10" s="6">
-        <v>10010050</v>
+        <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1340,7 +1340,7 @@
         <v>10060</v>
       </c>
       <c r="B11" s="6">
-        <v>10010060</v>
+        <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -1351,7 +1351,7 @@
         <v>10070</v>
       </c>
       <c r="B12" s="6">
-        <v>10010070</v>
+        <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
@@ -1362,7 +1362,7 @@
         <v>10080</v>
       </c>
       <c r="B13" s="6">
-        <v>10010080</v>
+        <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>18</v>
@@ -1373,7 +1373,7 @@
         <v>10090</v>
       </c>
       <c r="B14" s="6">
-        <v>10010090</v>
+        <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>19</v>
@@ -1384,7 +1384,7 @@
         <v>10100</v>
       </c>
       <c r="B15" s="6">
-        <v>10010100</v>
+        <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
@@ -1395,7 +1395,7 @@
         <v>10110</v>
       </c>
       <c r="B16" s="6">
-        <v>10010110</v>
+        <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
@@ -1406,7 +1406,7 @@
         <v>10120</v>
       </c>
       <c r="B17" s="6">
-        <v>10010120</v>
+        <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>22</v>
@@ -1417,7 +1417,7 @@
         <v>10130</v>
       </c>
       <c r="B18" s="6">
-        <v>10010130</v>
+        <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
@@ -1428,7 +1428,7 @@
         <v>10140</v>
       </c>
       <c r="B19" s="6">
-        <v>10010140</v>
+        <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>24</v>
@@ -1439,7 +1439,7 @@
         <v>10150</v>
       </c>
       <c r="B20" s="6">
-        <v>10010150</v>
+        <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>

--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>序号ID</t>
   </si>
@@ -179,34 +179,40 @@
     <t>12001_0_10000</t>
   </si>
   <si>
-    <t>12002_500</t>
-  </si>
-  <si>
-    <t>12002_1000</t>
-  </si>
-  <si>
-    <t>12002_2000</t>
-  </si>
-  <si>
-    <t>12002_3000</t>
-  </si>
-  <si>
-    <t>12002_5000</t>
-  </si>
-  <si>
-    <t>12002_7500</t>
-  </si>
-  <si>
-    <t>12002_10000</t>
-  </si>
-  <si>
-    <t>12002_12500</t>
-  </si>
-  <si>
-    <t>12002_15000</t>
+    <t>12002_20000</t>
   </si>
   <si>
     <t>12002_40000</t>
+  </si>
+  <si>
+    <t>12002_60000</t>
+  </si>
+  <si>
+    <t>12002_85000</t>
+  </si>
+  <si>
+    <t>12002_150000</t>
+  </si>
+  <si>
+    <t>12002_300000</t>
+  </si>
+  <si>
+    <t>12002_450000</t>
+  </si>
+  <si>
+    <t>12002_700000</t>
+  </si>
+  <si>
+    <t>12002_920000</t>
+  </si>
+  <si>
+    <t>12002_1250000</t>
+  </si>
+  <si>
+    <t>12002_1800000</t>
+  </si>
+  <si>
+    <t>12002_2500000</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1338,7 @@
         <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1343,7 +1349,7 @@
         <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1354,7 +1360,7 @@
         <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1365,7 +1371,7 @@
         <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1376,7 +1382,7 @@
         <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1387,7 +1393,7 @@
         <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1398,7 +1404,7 @@
         <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1409,7 +1415,7 @@
         <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1420,7 +1426,7 @@
         <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1431,7 +1437,7 @@
         <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1442,7 +1448,7 @@
         <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -149,7 +149,7 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>list&lt;String&gt;{;}</t>
+    <t>string</t>
   </si>
   <si>
     <t>map&lt;int{_}int&gt;{;}</t>
@@ -167,7 +167,7 @@
     <t>triggerType</t>
   </si>
   <si>
-    <t>12001_0_100000</t>
+    <t>effectiveBetAll(0,100000)</t>
   </si>
   <si>
     <t>10001_1000</t>
@@ -176,43 +176,43 @@
     <t>100006_100007_100008_100009_100010</t>
   </si>
   <si>
-    <t>12001_0_10000</t>
-  </si>
-  <si>
-    <t>12002_20000</t>
-  </si>
-  <si>
-    <t>12002_40000</t>
-  </si>
-  <si>
-    <t>12002_60000</t>
-  </si>
-  <si>
-    <t>12002_85000</t>
-  </si>
-  <si>
-    <t>12002_150000</t>
-  </si>
-  <si>
-    <t>12002_300000</t>
-  </si>
-  <si>
-    <t>12002_450000</t>
-  </si>
-  <si>
-    <t>12002_700000</t>
-  </si>
-  <si>
-    <t>12002_920000</t>
-  </si>
-  <si>
-    <t>12002_1250000</t>
-  </si>
-  <si>
-    <t>12002_1800000</t>
-  </si>
-  <si>
-    <t>12002_2500000</t>
+    <t>effectiveBetAll(0,10000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(20000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(40000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(60000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(85000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(150000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(300000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(450000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(700000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(920000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1250000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1800000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2500000)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -890,6 +890,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1248,7 +1251,7 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1275,11 +1278,11 @@
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <v>100011</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1290,7 +1293,7 @@
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -1300,7 +1303,7 @@
       <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1308,99 +1311,99 @@
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <v>100011</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>10040</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1411,7 +1414,7 @@
       <c r="A17" s="2">
         <v>10120</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1422,7 +1425,7 @@
       <c r="A18" s="2">
         <v>10130</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1433,7 +1436,7 @@
       <c r="A19" s="2">
         <v>10140</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1444,7 +1447,7 @@
       <c r="A20" s="2">
         <v>10150</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">

--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -179,40 +179,40 @@
     <t>effectiveBetAll(0,10000)</t>
   </si>
   <si>
-    <t>effectiveBet(20000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(40000)</t>
-  </si>
-  <si>
     <t>effectiveBet(60000)</t>
   </si>
   <si>
-    <t>effectiveBet(85000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(150000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(300000)</t>
+    <t>effectiveBet(120000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(180000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(255000)</t>
   </si>
   <si>
     <t>effectiveBet(450000)</t>
   </si>
   <si>
-    <t>effectiveBet(700000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(920000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(1250000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(1800000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(2500000)</t>
+    <t>effectiveBet(900000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1350000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2100000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2760000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(3750000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(5400000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(7500000)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -895,6 +895,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,8 +1212,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
@@ -1230,7 +1233,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1244,7 +1247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1272,13 +1275,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1288,8 +1291,10 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:4">
+      <c r="D5" s="8"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:5">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1298,8 +1303,9 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:4">
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:5">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1309,9 +1315,10 @@
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="8"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1321,8 +1328,10 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="8"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
@@ -1333,7 +1342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
@@ -1343,8 +1352,9 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
@@ -1354,8 +1364,9 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
@@ -1365,8 +1376,9 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
@@ -1376,8 +1388,9 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
@@ -1387,8 +1400,9 @@
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
@@ -1398,8 +1412,9 @@
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
@@ -1409,8 +1424,9 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
@@ -1420,8 +1436,9 @@
       <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
@@ -1431,8 +1448,9 @@
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
@@ -1442,8 +1460,9 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
@@ -1453,6 +1472,7 @@
       <c r="C20" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/dropConfig.xlsx
+++ b/slots/resources/sample/dropConfig.xlsx
@@ -179,40 +179,40 @@
     <t>effectiveBetAll(0,10000)</t>
   </si>
   <si>
+    <t>effectiveBet(20000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(40000)</t>
+  </si>
+  <si>
     <t>effectiveBet(60000)</t>
   </si>
   <si>
-    <t>effectiveBet(120000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(180000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(255000)</t>
+    <t>effectiveBet(85000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(150000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(300000)</t>
   </si>
   <si>
     <t>effectiveBet(450000)</t>
   </si>
   <si>
-    <t>effectiveBet(900000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(1350000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(2100000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(2760000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(3750000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(5400000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(7500000)</t>
+    <t>effectiveBet(700000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(920000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1250000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1800000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2500000)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -895,9 +895,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,8 +1209,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
@@ -1233,7 +1230,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1247,7 +1244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1261,7 +1258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1275,13 +1272,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1291,10 +1288,8 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:5">
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1303,9 +1298,8 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:5">
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:4">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1315,10 +1309,9 @@
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1328,10 +1321,8 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
@@ -1342,7 +1333,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
@@ -1352,9 +1343,8 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
@@ -1364,9 +1354,8 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:5">
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
@@ -1376,9 +1365,8 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
@@ -1388,9 +1376,8 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:5">
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
@@ -1400,9 +1387,8 @@
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:5">
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
@@ -1412,9 +1398,8 @@
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:5">
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
@@ -1424,9 +1409,8 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
@@ -1436,9 +1420,8 @@
       <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:4">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
@@ -1448,9 +1431,8 @@
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
@@ -1460,9 +1442,8 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
@@ -1472,7 +1453,6 @@
       <c r="C20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
